--- a/tbl_pnl_dashboard_completed.xlsx
+++ b/tbl_pnl_dashboard_completed.xlsx
@@ -1,79 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rudra S Divey\Desktop\NSE_Project\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234CFF9A-E7A2-40AA-8E57-47508914E398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="25920" windowHeight="15566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="tbl_pnl_dashboard" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tbl_pnl_dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
-  <si>
-    <t>For the day ended Jan 1,2026</t>
-  </si>
-  <si>
-    <t>For the week ended Jan 1,2026</t>
-  </si>
-  <si>
-    <t>For the month  ended Jan 1,2026</t>
-  </si>
-  <si>
-    <t>NSE</t>
-  </si>
-  <si>
-    <t>BSE</t>
-  </si>
-  <si>
-    <t>Average Daily Volume :(In Crores)</t>
-  </si>
-  <si>
-    <t>Cash Market : Turnover</t>
-  </si>
-  <si>
-    <t>Futures : Turnover</t>
-  </si>
-  <si>
-    <t>Options : Premium Turnover</t>
-  </si>
-  <si>
-    <t>For the quarter ended Jan 1,2026</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -81,30 +66,119 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -392,165 +466,1681 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C6:K12"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A6:K63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="38.921875" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="23.4609375" customWidth="1"/>
-    <col min="6" max="6" width="27.69140625" customWidth="1"/>
-    <col min="7" max="7" width="22.921875" customWidth="1"/>
-    <col min="8" max="8" width="27.84375" customWidth="1"/>
-    <col min="9" max="9" width="29.15234375" customWidth="1"/>
-    <col min="10" max="10" width="23.921875" customWidth="1"/>
-    <col min="11" max="11" width="31.69140625" customWidth="1"/>
+    <col width="52" customWidth="1" style="2" min="3" max="3"/>
+    <col width="14" customWidth="1" style="2" min="4" max="4"/>
+    <col width="14" customWidth="1" style="2" min="5" max="5"/>
+    <col width="14" customWidth="1" style="2" min="6" max="6"/>
+    <col width="14" customWidth="1" style="2" min="7" max="7"/>
+    <col width="14" customWidth="1" style="2" min="8" max="8"/>
+    <col width="14" customWidth="1" style="2" min="9" max="9"/>
+    <col width="14" customWidth="1" style="2" min="10" max="10"/>
+    <col width="14" customWidth="1" style="2" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.4">
-      <c r="D6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.4">
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.4">
-      <c r="D8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.4">
-      <c r="C9" t="s">
+    <row r="6">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>For the day ended Jan 1,2026</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>For the week ended Jan 1,2026</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>For the month  ended Jan 1,2026</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>For the quarter ended Jan 1,2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Average Daily Volume :(In Crores)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Cash Market : Turnover</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>1200.5</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>780.33</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>1218.51</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>795.9299999999999</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1250.92</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>835.55</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>1298.94</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>860.76</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Futures : Turnover</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>3400.25</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>2210.16</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>3451.25</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>2254.37</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>3543.06</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>2366.57</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>3679.07</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>2437.98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Options : Premium Turnover</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>9800.75</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>6370.49</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>9947.76</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>6497.9</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>10212.38</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>6821.32</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>10604.41</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>7027.14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Currency Futures : Turnover</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>520</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>338</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>527.8</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>344.76</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>541.84</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>361.92</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>562.64</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>372.84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Currency Options : Turnover</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>201.83</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>315.16</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>205.86</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>323.54</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>216.11</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>335.96</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>222.63</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Transaction Charges :(In Crores)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Cash Markets</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>47.41</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>32.62</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Futures</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>73.29000000000001</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>114.44</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>117.49</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>78.47</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>80.84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Options</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>280.25</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>182.16</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>284.45</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>185.81</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>292.02</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>195.05</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>303.23</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>200.94</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Currency Derivatives</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>13.26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Others(IRF, WDM, Commodity, Mutual Fund)</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>6.63</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Total Transaction Charges</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>466.25</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>303.06</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>473.24</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>309.12</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>485.83</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>324.51</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>504.48</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>334.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Operating Income :(In Crores)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Listing Services</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>16.13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Data Centre and Connectivity Charges</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>25.63</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Operating Investment Income</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>13.09</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Other Operating Income</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>8.960000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Total Operating Income</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>555.25</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>360.91</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>563.58</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>368.13</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>578.5700000000001</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>386.45</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>600.78</v>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>398.11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Non-Operating Income :(In Crores)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Interest &amp; Other Investment Income</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>44.55</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>30.65</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Subsidiary Dividend</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Total Non Operting Income</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>68.77</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>71.41</v>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>47.32</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>621.25</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>403.81</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>630.5700000000001</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>411.89</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>647.34</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>432.39</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>672.1900000000001</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>445.44</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Expenditure :(In Crores)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="6" t="n"/>
+      <c r="J34" s="6" t="n"/>
+      <c r="K34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Empolyee Expenses</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>56.69</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Clearing and Settlement Charges</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="J36" s="8" t="n">
+        <v>34.89</v>
+      </c>
+      <c r="K36" s="8" t="n">
+        <v>23.12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Regulatory Expenses</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>20.61</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>SEBI Settlement Fees / Penalty / Provisions</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="K38" s="8" t="n">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Depriciation</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="K39" s="8" t="n">
+        <v>15.77</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Technology Expenses</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <v>32.44</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Other Variable Expense - SMS &amp; LES, License Fees for Index</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>10.58</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="K42" s="8" t="n">
+        <v>13.26</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Total Expenditure</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>252.5</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>164.12</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>256.29</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>167.41</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>263.11</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>175.74</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>273.21</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <v>181.04</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Profit :(In Crores)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Profit Before Tax Before IPFT and SGF Contribution</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>239.69</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>374.28</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>244.48</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>384.24</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>256.65</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>398.99</v>
+      </c>
+      <c r="K45" s="8" t="n">
+        <v>264.39</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Less : Contribution to IPFT</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>8.960000000000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Less : Provision: Contribution to Core SGF</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="K47" s="8" t="n">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Profit Before Exceptional Items</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>348</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>226.2</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>353.22</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>230.72</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>362.62</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>242.21</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="K48" s="8" t="n">
+        <v>249.52</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Less Exceptional Items</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.4">
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>1200.5</v>
-      </c>
-      <c r="E10">
-        <v>800.25</v>
-      </c>
-      <c r="F10">
-        <v>1218.75</v>
-      </c>
-      <c r="G10">
-        <v>812.6</v>
-      </c>
-      <c r="H10">
-        <v>1250</v>
-      </c>
-      <c r="I10">
-        <v>835.75</v>
-      </c>
-      <c r="J10">
-        <v>1300</v>
-      </c>
-      <c r="K10">
-        <v>860.5</v>
-      </c>
-    </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.4">
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11">
-        <v>3400.25</v>
-      </c>
-      <c r="E11">
-        <v>2100.5</v>
-      </c>
-      <c r="F11">
-        <v>3435.5</v>
-      </c>
-      <c r="G11">
-        <v>2125.75</v>
-      </c>
-      <c r="H11">
-        <v>3500</v>
-      </c>
-      <c r="I11">
-        <v>2195.25</v>
-      </c>
-      <c r="J11">
-        <v>3600</v>
-      </c>
-      <c r="K11">
-        <v>2250.7510000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.4">
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12">
-        <v>9800.75</v>
-      </c>
-      <c r="E12">
-        <v>5600.25</v>
-      </c>
-      <c r="F12">
-        <v>9855.25</v>
-      </c>
-      <c r="G12">
-        <v>5645.5</v>
-      </c>
-      <c r="H12">
-        <v>9900</v>
-      </c>
-      <c r="I12">
-        <v>5750.5</v>
-      </c>
-      <c r="J12">
-        <v>10000</v>
-      </c>
-      <c r="K12">
-        <v>5900.25</v>
+      <c r="E49" s="8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="I49" s="8" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="K49" s="8" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Profit Before Tax</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>343</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>222.95</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>348.14</v>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>227.41</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>357.41</v>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>238.73</v>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>371.13</v>
+      </c>
+      <c r="K50" s="8" t="n">
+        <v>245.93</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Provision for Tax</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>89.83</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>92.22</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>63.45</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Profit After Tax</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>165.43</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>258.32</v>
+      </c>
+      <c r="G52" s="8" t="n">
+        <v>168.73</v>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>265.19</v>
+      </c>
+      <c r="I52" s="8" t="n">
+        <v>177.13</v>
+      </c>
+      <c r="J52" s="8" t="n">
+        <v>275.37</v>
+      </c>
+      <c r="K52" s="8" t="n">
+        <v>182.48</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Additional Metrics</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6" t="n"/>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Expenditure Linked to Revenue</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>117.16</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>182.95</v>
+      </c>
+      <c r="G54" s="8" t="n">
+        <v>119.51</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>187.82</v>
+      </c>
+      <c r="I54" s="8" t="n">
+        <v>125.45</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>195.03</v>
+      </c>
+      <c r="K54" s="8" t="n">
+        <v>129.24</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>% of Operating Revenue</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="I55" s="8" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>35.16</v>
+      </c>
+      <c r="K55" s="8" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Balance Expenditure</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>46.96</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>75.28</v>
+      </c>
+      <c r="I56" s="8" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="J56" s="8" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="K56" s="8" t="n">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>% of Operating Revenue</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="K57" s="8" t="n">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Operating Profit</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>303</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>196.95</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>307.54</v>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>200.89</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>315.73</v>
+      </c>
+      <c r="I58" s="8" t="n">
+        <v>210.89</v>
+      </c>
+      <c r="J58" s="8" t="n">
+        <v>327.85</v>
+      </c>
+      <c r="K58" s="8" t="n">
+        <v>217.25</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Operating Profit Margin (%)</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="I59" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="K59" s="8" t="n">
+        <v>39.15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Operating EBITDA</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>325</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>211.25</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>329.87</v>
+      </c>
+      <c r="G60" s="8" t="n">
+        <v>215.48</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>338.65</v>
+      </c>
+      <c r="I60" s="8" t="n">
+        <v>226.2</v>
+      </c>
+      <c r="J60" s="8" t="n">
+        <v>351.65</v>
+      </c>
+      <c r="K60" s="8" t="n">
+        <v>233.02</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Operating EBITDA Margin (%)</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="K61" s="8" t="n">
+        <v>41.94</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Profit Before Tax Margin (%)</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>62.73</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>40.97</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="J62" s="8" t="n">
+        <v>66.87</v>
+      </c>
+      <c r="K62" s="8" t="n">
+        <v>44.31</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>PAT Margin (%)</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>46.59</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>47.83</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="J63" s="8" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="K63" s="8" t="n">
+        <v>32.91</v>
       </c>
     </row>
   </sheetData>
